--- a/research/traditional_assets/database/data/greece/greece_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_business_consumer_services.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.02056451612903226</v>
+        <v>-0.1159663865546219</v>
       </c>
       <c r="H2">
-        <v>-0.02056451612903226</v>
+        <v>-0.1159663865546219</v>
       </c>
       <c r="I2">
-        <v>-0.03431025623148135</v>
+        <v>-0.1830718630837107</v>
       </c>
       <c r="J2">
-        <v>-0.03431025623148135</v>
+        <v>-0.1830718630837107</v>
       </c>
       <c r="K2">
-        <v>-0.102</v>
+        <v>-0.384</v>
       </c>
       <c r="L2">
-        <v>-0.04112903225806452</v>
+        <v>-0.1613445378151261</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,55 +627,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.396</v>
+        <v>0.152</v>
       </c>
       <c r="V2">
-        <v>0.03666666666666667</v>
+        <v>0.04075067024128686</v>
       </c>
       <c r="W2">
-        <v>-0.2035928143712575</v>
+        <v>-0.5196211096075778</v>
       </c>
       <c r="X2">
-        <v>0.1605293913657729</v>
+        <v>0.1177959045797525</v>
       </c>
       <c r="Y2">
-        <v>-0.3641222057370304</v>
+        <v>-0.6374170141873303</v>
       </c>
       <c r="Z2">
-        <v>84.21859851726798</v>
+        <v>6.674983833085801</v>
       </c>
       <c r="AA2">
-        <v>-2.88956169458372</v>
+        <v>-1.222001726376666</v>
       </c>
       <c r="AB2">
-        <v>0.160045460847304</v>
+        <v>0.1177963370548795</v>
       </c>
       <c r="AC2">
-        <v>-3.049607155431024</v>
+        <v>-1.339798063431546</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.06544717727036872</v>
+        <v>0.01355517069615758</v>
       </c>
       <c r="AF2">
-        <v>0.06544717727036872</v>
+        <v>0.01355517069615758</v>
       </c>
       <c r="AG2">
-        <v>-0.3305528227296313</v>
+        <v>-0.1384448293038424</v>
       </c>
       <c r="AH2">
-        <v>0.00602342234080148</v>
+        <v>0.00362093520145366</v>
       </c>
       <c r="AI2">
-        <v>0.0813567119378087</v>
+        <v>0.04901434553559737</v>
       </c>
       <c r="AJ2">
-        <v>-0.03157309236415806</v>
+        <v>-0.03854732079112331</v>
       </c>
       <c r="AK2">
-        <v>-0.8092914852263116</v>
+        <v>-1.111514106801455</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>6.356785052492908</v>
+        <v>0.3624210191200063</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.02056451612903226</v>
+        <v>-0.1159663865546219</v>
       </c>
       <c r="H3">
-        <v>-0.02056451612903226</v>
+        <v>-0.1159663865546219</v>
       </c>
       <c r="I3">
-        <v>-0.03431025623148135</v>
+        <v>-0.1830718630837107</v>
       </c>
       <c r="J3">
-        <v>-0.03431025623148135</v>
+        <v>-0.1830718630837107</v>
       </c>
       <c r="K3">
-        <v>-0.102</v>
+        <v>-0.384</v>
       </c>
       <c r="L3">
-        <v>-0.04112903225806452</v>
+        <v>-0.1613445378151261</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,55 +746,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.396</v>
+        <v>0.152</v>
       </c>
       <c r="V3">
-        <v>0.03666666666666667</v>
+        <v>0.04075067024128686</v>
       </c>
       <c r="W3">
-        <v>-0.2035928143712575</v>
+        <v>-0.5196211096075778</v>
       </c>
       <c r="X3">
-        <v>0.1605293913657729</v>
+        <v>0.1177959045797525</v>
       </c>
       <c r="Y3">
-        <v>-0.3641222057370304</v>
+        <v>-0.6374170141873303</v>
       </c>
       <c r="Z3">
-        <v>84.21859851726798</v>
+        <v>6.674983833085801</v>
       </c>
       <c r="AA3">
-        <v>-2.88956169458372</v>
+        <v>-1.222001726376666</v>
       </c>
       <c r="AB3">
-        <v>0.160045460847304</v>
+        <v>0.1177963370548795</v>
       </c>
       <c r="AC3">
-        <v>-3.049607155431024</v>
+        <v>-1.339798063431546</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.06544717727036872</v>
+        <v>0.01355517069615758</v>
       </c>
       <c r="AF3">
-        <v>0.06544717727036872</v>
+        <v>0.01355517069615758</v>
       </c>
       <c r="AG3">
-        <v>-0.3305528227296313</v>
+        <v>-0.1384448293038424</v>
       </c>
       <c r="AH3">
-        <v>0.00602342234080148</v>
+        <v>0.00362093520145366</v>
       </c>
       <c r="AI3">
-        <v>0.0813567119378087</v>
+        <v>0.04901434553559737</v>
       </c>
       <c r="AJ3">
-        <v>-0.03157309236415806</v>
+        <v>-0.03854732079112331</v>
       </c>
       <c r="AK3">
-        <v>-0.8092914852263116</v>
+        <v>-1.111514106801455</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>6.356785052492908</v>
+        <v>0.3624210191200063</v>
       </c>
     </row>
   </sheetData>
